--- a/data/trans_orig/P71_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>57306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423562</t>
+          <t>423783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446377</t>
+          <t>446222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>249662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273199</t>
+          <t>273201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680366</t>
+          <t>680623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>714107</t>
+          <t>713115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34402</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59833</t>
+          <t>60889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57173</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86295</t>
+          <t>87275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97945</t>
+          <t>95824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137213</t>
+          <t>136812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>301377</t>
+          <t>300321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326808</t>
+          <t>327447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279820</t>
+          <t>278840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308942</t>
+          <t>309139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>590112</t>
+          <t>590513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629380</t>
+          <t>631501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>65210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>97420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47749</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96460</t>
+          <t>98272</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134651</t>
+          <t>136905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437077</t>
+          <t>436188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>469078</t>
+          <t>468398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117104</t>
+          <t>117972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138891</t>
+          <t>139118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563809</t>
+          <t>561555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>602000</t>
+          <t>600188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>247502</t>
+          <t>246099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306005</t>
+          <t>304639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153065</t>
+          <t>154726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201800</t>
+          <t>201114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416065</t>
+          <t>416157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488824</t>
+          <t>489573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915814</t>
+          <t>917180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>974317</t>
+          <t>975720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490665</t>
+          <t>491351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539400</t>
+          <t>537739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1425460</t>
+          <t>1424711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1498219</t>
+          <t>1498127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100674</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>135090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173939</t>
+          <t>171531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218070</t>
+          <t>217591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284939</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344228</t>
+          <t>342907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211742</t>
+          <t>211290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245706</t>
+          <t>247197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>335452</t>
+          <t>335931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379583</t>
+          <t>381991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>555674</t>
+          <t>556995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>614963</t>
+          <t>617015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47178</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>367682</t>
+          <t>369742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>433972</t>
+          <t>436227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>398560</t>
+          <t>403962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>469617</t>
+          <t>472641</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246402</t>
+          <t>248083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268973</t>
+          <t>269157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>800427</t>
+          <t>798172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>866717</t>
+          <t>864657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1058362</t>
+          <t>1055338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1129419</t>
+          <t>1124017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543525</t>
+          <t>541533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>632497</t>
+          <t>630352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>869961</t>
+          <t>869008</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>972030</t>
+          <t>973268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1443011</t>
+          <t>1440346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1574333</t>
+          <t>1576261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2591979</t>
+          <t>2594124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2680951</t>
+          <t>2682943</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2341865</t>
+          <t>2340627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2443934</t>
+          <t>2444887</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4964038</t>
+          <t>4962110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5095360</t>
+          <t>5098025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>49527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81837</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60937</t>
+          <t>60995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89076</t>
+          <t>91600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133907</t>
+          <t>133068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352183</t>
+          <t>353530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384003</t>
+          <t>384493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252498</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280243</t>
+          <t>280046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>613548</t>
+          <t>614387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>658379</t>
+          <t>655855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>44349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73300</t>
+          <t>73376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>44090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74990</t>
+          <t>72171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96328</t>
+          <t>96073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>138804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340426</t>
+          <t>340350</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369983</t>
+          <t>369377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262086</t>
+          <t>264905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291955</t>
+          <t>292986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613195</t>
+          <t>611998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>654474</t>
+          <t>654729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190239</t>
+          <t>189994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241384</t>
+          <t>238100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60792</t>
+          <t>60307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>90726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259307</t>
+          <t>260323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316715</t>
+          <t>317915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387009</t>
+          <t>390293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438154</t>
+          <t>438399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168223</t>
+          <t>167537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197471</t>
+          <t>197956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569941</t>
+          <t>568741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627349</t>
+          <t>626333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409119</t>
+          <t>409413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>477998</t>
+          <t>477579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250821</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308096</t>
+          <t>307187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>680450</t>
+          <t>679871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>766858</t>
+          <t>766287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675548</t>
+          <t>675967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744427</t>
+          <t>744133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>456639</t>
+          <t>457548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513914</t>
+          <t>514735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151422</t>
+          <t>1151993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1237830</t>
+          <t>1238409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188753</t>
+          <t>188294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234232</t>
+          <t>233146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285688</t>
+          <t>285620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343319</t>
+          <t>342706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>489540</t>
+          <t>487187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>559672</t>
+          <t>561128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276364</t>
+          <t>277450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321843</t>
+          <t>322302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415053</t>
+          <t>415666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>472684</t>
+          <t>472752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709296</t>
+          <t>707840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>779428</t>
+          <t>781781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68864</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312699</t>
+          <t>317391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>378704</t>
+          <t>378127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>368379</t>
+          <t>367311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>433309</t>
+          <t>437820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195132</t>
+          <t>197530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222250</t>
+          <t>221857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>723953</t>
+          <t>724530</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>789958</t>
+          <t>785266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>933344</t>
+          <t>928833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998274</t>
+          <t>999342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>981170</t>
+          <t>985918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1096333</t>
+          <t>1095882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1064710</t>
+          <t>1053235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1179254</t>
+          <t>1173454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2069623</t>
+          <t>2078477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2235419</t>
+          <t>2237138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2307943</t>
+          <t>2308394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2423106</t>
+          <t>2418358</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2355284</t>
+          <t>2361084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2469828</t>
+          <t>2481303</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4703395</t>
+          <t>4701676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4869191</t>
+          <t>4860337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58949</t>
+          <t>58758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118755</t>
+          <t>116992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356497</t>
+          <t>355379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384885</t>
+          <t>383553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288106</t>
+          <t>288297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311994</t>
+          <t>313075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652699</t>
+          <t>654462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690824</t>
+          <t>689851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68188</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100676</t>
+          <t>101489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77086</t>
+          <t>77433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113880</t>
+          <t>114346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154166</t>
+          <t>153960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201738</t>
+          <t>200833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274724</t>
+          <t>273911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307212</t>
+          <t>307821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256763</t>
+          <t>256297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293557</t>
+          <t>293210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544305</t>
+          <t>545210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>591877</t>
+          <t>592083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171017</t>
+          <t>171230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214188</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>66846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224036</t>
+          <t>222209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278975</t>
+          <t>275099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303608</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346779</t>
+          <t>346566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95922</t>
+          <t>96318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120859</t>
+          <t>120548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401985</t>
+          <t>405861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456924</t>
+          <t>458751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>408151</t>
+          <t>404347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476799</t>
+          <t>472699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289647</t>
+          <t>290021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>346558</t>
+          <t>345007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>713166</t>
+          <t>711422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>802223</t>
+          <t>800983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664709</t>
+          <t>668809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>733357</t>
+          <t>737161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474277</t>
+          <t>475828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>531188</t>
+          <t>530814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160120</t>
+          <t>1161360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1249177</t>
+          <t>1250921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264887</t>
+          <t>269350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318513</t>
+          <t>317456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>365767</t>
+          <t>368008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>420547</t>
+          <t>422095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>647073</t>
+          <t>648051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>722348</t>
+          <t>723841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296374</t>
+          <t>297431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>345537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316773</t>
+          <t>315225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371553</t>
+          <t>369312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>629859</t>
+          <t>628366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>705134</t>
+          <t>704156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51830</t>
+          <t>49992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80990</t>
+          <t>80240</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>321947</t>
+          <t>324739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>387579</t>
+          <t>389136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>383577</t>
+          <t>383879</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>456497</t>
+          <t>451080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203674</t>
+          <t>204424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232834</t>
+          <t>234672</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687250</t>
+          <t>685693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>752882</t>
+          <t>750090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>902996</t>
+          <t>908413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975916</t>
+          <t>975614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1073694</t>
+          <t>1069232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1183343</t>
+          <t>1179698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1202114</t>
+          <t>1202382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1320582</t>
+          <t>1320028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2305511</t>
+          <t>2308755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2462635</t>
+          <t>2465560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2175311</t>
+          <t>2178956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2284960</t>
+          <t>2289422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2193264</t>
+          <t>2193818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2311732</t>
+          <t>2311464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4409865</t>
+          <t>4406940</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4566989</t>
+          <t>4563745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36156</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52614</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467092</t>
+          <t>466774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487398</t>
+          <t>487296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421464</t>
+          <t>422112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435151</t>
+          <t>435293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>895752</t>
+          <t>895787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>919986</t>
+          <t>918872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56743</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424865</t>
+          <t>424238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440538</t>
+          <t>441260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346366</t>
+          <t>346685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363418</t>
+          <t>363451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>775104</t>
+          <t>777181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799632</t>
+          <t>801237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>21259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>94388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114826</t>
+          <t>110772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573869</t>
+          <t>573071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647614</t>
+          <t>646200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139019</t>
+          <t>139188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152178</t>
+          <t>151841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>718426</t>
+          <t>722480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>800301</t>
+          <t>801213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132629</t>
+          <t>131912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187644</t>
+          <t>186070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159359</t>
+          <t>159376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180461</t>
+          <t>186128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>319641</t>
+          <t>321282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>837300</t>
+          <t>838874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892315</t>
+          <t>893032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>813005</t>
+          <t>812988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>907337</t>
+          <t>908357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1677667</t>
+          <t>1676026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1816847</t>
+          <t>1811180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98789</t>
+          <t>97665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136736</t>
+          <t>136005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223253</t>
+          <t>223549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>432141</t>
+          <t>420355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>336154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>571267</t>
+          <t>544307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331717</t>
+          <t>332448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369664</t>
+          <t>370788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370788</t>
+          <t>382574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579676</t>
+          <t>579380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700115</t>
+          <t>727075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>935389</t>
+          <t>935228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>50793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>110919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152194</t>
+          <t>151266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136020</t>
+          <t>136672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>188200</t>
+          <t>189004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172958</t>
+          <t>171101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205385</t>
+          <t>204780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>595975</t>
+          <t>596903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>636602</t>
+          <t>637250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>781863</t>
+          <t>781059</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>834043</t>
+          <t>833391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>311316</t>
+          <t>308212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>450132</t>
+          <t>451790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>491141</t>
+          <t>491675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>776631</t>
+          <t>787592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>868009</t>
+          <t>866071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1215053</t>
+          <t>1186683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2886925</t>
+          <t>2885267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3025741</t>
+          <t>3028845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2738530</t>
+          <t>2727569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3024020</t>
+          <t>3023486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5637165</t>
+          <t>5665535</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5984209</t>
+          <t>5986147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52880</t>
+          <t>55070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89798</t>
+          <t>89021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423783</t>
+          <t>422866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446222</t>
+          <t>446510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249662</t>
+          <t>247472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273201</t>
+          <t>273051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680623</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713115</t>
+          <t>715683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87275</t>
+          <t>86761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95824</t>
+          <t>96282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136812</t>
+          <t>137651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300321</t>
+          <t>302012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327447</t>
+          <t>326654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278840</t>
+          <t>279354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309139</t>
+          <t>310210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>590513</t>
+          <t>589674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>631501</t>
+          <t>631043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65210</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97420</t>
+          <t>95684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46881</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98272</t>
+          <t>96141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136905</t>
+          <t>135374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436188</t>
+          <t>437924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468398</t>
+          <t>469910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117972</t>
+          <t>118160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139118</t>
+          <t>138434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561555</t>
+          <t>563086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600188</t>
+          <t>602319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246099</t>
+          <t>247312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304639</t>
+          <t>305111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>154694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201114</t>
+          <t>200991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416157</t>
+          <t>416178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>489573</t>
+          <t>489190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917180</t>
+          <t>916708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>975720</t>
+          <t>974507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>491351</t>
+          <t>491474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537739</t>
+          <t>537771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1424711</t>
+          <t>1425094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1498127</t>
+          <t>1498106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135090</t>
+          <t>134610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171531</t>
+          <t>176477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217591</t>
+          <t>222032</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282887</t>
+          <t>285183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342907</t>
+          <t>343790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211290</t>
+          <t>211770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>247197</t>
+          <t>246530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>335931</t>
+          <t>331490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381991</t>
+          <t>377045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>556995</t>
+          <t>556112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617015</t>
+          <t>614719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>46533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>369742</t>
+          <t>372366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>436227</t>
+          <t>438548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>403962</t>
+          <t>402251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>472641</t>
+          <t>472578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248083</t>
+          <t>247047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269157</t>
+          <t>268654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>798172</t>
+          <t>795851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>864657</t>
+          <t>862033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1055338</t>
+          <t>1055401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1124017</t>
+          <t>1125728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541533</t>
+          <t>538069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>630352</t>
+          <t>627911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>869008</t>
+          <t>873087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>973268</t>
+          <t>977322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1440346</t>
+          <t>1438974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1576261</t>
+          <t>1574629</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2594124</t>
+          <t>2596565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2682943</t>
+          <t>2686407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2340627</t>
+          <t>2336573</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2444887</t>
+          <t>2440808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4962110</t>
+          <t>4963742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5098025</t>
+          <t>5099397</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49527</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80490</t>
+          <t>81508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>59902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91600</t>
+          <t>89155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133068</t>
+          <t>131029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353530</t>
+          <t>352512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384493</t>
+          <t>384004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>253533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280046</t>
+          <t>280770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614387</t>
+          <t>616426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655855</t>
+          <t>658300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44349</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73376</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>44721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72171</t>
+          <t>73462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>95335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138804</t>
+          <t>139380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340350</t>
+          <t>340631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369377</t>
+          <t>369891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264905</t>
+          <t>263614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292986</t>
+          <t>292355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>611998</t>
+          <t>611422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>654729</t>
+          <t>655467</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189994</t>
+          <t>189142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>238100</t>
+          <t>239431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60307</t>
+          <t>59387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90726</t>
+          <t>89842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260323</t>
+          <t>261050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317915</t>
+          <t>316721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390293</t>
+          <t>388962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438399</t>
+          <t>439251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167537</t>
+          <t>168421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197956</t>
+          <t>198876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568741</t>
+          <t>569935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>626333</t>
+          <t>625606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409413</t>
+          <t>409291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>477579</t>
+          <t>477180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>252244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307187</t>
+          <t>307249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>679871</t>
+          <t>678723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>766287</t>
+          <t>765093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675967</t>
+          <t>676366</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744133</t>
+          <t>744255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>457548</t>
+          <t>457486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514735</t>
+          <t>512491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151993</t>
+          <t>1153187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238409</t>
+          <t>1239557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188294</t>
+          <t>188704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>233146</t>
+          <t>232984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285620</t>
+          <t>285675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342706</t>
+          <t>342211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>487187</t>
+          <t>489764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>561128</t>
+          <t>559050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277450</t>
+          <t>277612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322302</t>
+          <t>321892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415666</t>
+          <t>416161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>472752</t>
+          <t>472697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707840</t>
+          <t>709918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>781781</t>
+          <t>779204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>42005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66466</t>
+          <t>67755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>317391</t>
+          <t>314530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>378127</t>
+          <t>378276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367311</t>
+          <t>366130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>437820</t>
+          <t>434822</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197530</t>
+          <t>196241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221857</t>
+          <t>221991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>724530</t>
+          <t>724381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>785266</t>
+          <t>788127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>928833</t>
+          <t>931831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>999342</t>
+          <t>1000523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>985918</t>
+          <t>989142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1095882</t>
+          <t>1093214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1053235</t>
+          <t>1052200</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1173454</t>
+          <t>1172455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2078477</t>
+          <t>2072517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2237138</t>
+          <t>2236155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2308394</t>
+          <t>2311062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2418358</t>
+          <t>2415134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2361084</t>
+          <t>2362083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2481303</t>
+          <t>2482338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4701676</t>
+          <t>4702659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4860337</t>
+          <t>4866297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,13%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>39109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>68014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58758</t>
+          <t>59252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>79902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116992</t>
+          <t>116848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355379</t>
+          <t>356385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383553</t>
+          <t>385290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288297</t>
+          <t>287803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313075</t>
+          <t>312586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654462</t>
+          <t>654606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689851</t>
+          <t>691552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>68729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101489</t>
+          <t>102384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>78407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114346</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153960</t>
+          <t>153403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200833</t>
+          <t>202895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273911</t>
+          <t>273016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307821</t>
+          <t>306671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256297</t>
+          <t>259444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293210</t>
+          <t>292236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545210</t>
+          <t>543148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>592083</t>
+          <t>592640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171230</t>
+          <t>170027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214180</t>
+          <t>217356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42616</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66846</t>
+          <t>68166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222209</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275099</t>
+          <t>271955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303616</t>
+          <t>300440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346566</t>
+          <t>347769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96318</t>
+          <t>94998</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120548</t>
+          <t>120501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>405861</t>
+          <t>409005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>458751</t>
+          <t>457546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>404347</t>
+          <t>408991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>472699</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290021</t>
+          <t>289151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345007</t>
+          <t>342410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711422</t>
+          <t>712167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>800983</t>
+          <t>800142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>668809</t>
+          <t>669032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>737161</t>
+          <t>732517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>475828</t>
+          <t>478425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>530814</t>
+          <t>531684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161360</t>
+          <t>1162201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1250921</t>
+          <t>1250176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269350</t>
+          <t>265762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317456</t>
+          <t>315368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368008</t>
+          <t>366528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422095</t>
+          <t>418926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>648051</t>
+          <t>646146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>723841</t>
+          <t>717627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297431</t>
+          <t>299519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345537</t>
+          <t>349125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315225</t>
+          <t>318394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>369312</t>
+          <t>370792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>628366</t>
+          <t>634580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>704156</t>
+          <t>706061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>324739</t>
+          <t>323664</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>389136</t>
+          <t>386447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>383879</t>
+          <t>386426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>451080</t>
+          <t>455848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234672</t>
+          <t>234027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>685693</t>
+          <t>688382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>750090</t>
+          <t>751165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>908413</t>
+          <t>903645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975614</t>
+          <t>973067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1069232</t>
+          <t>1074034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1179698</t>
+          <t>1187306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1202382</t>
+          <t>1199939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1320028</t>
+          <t>1312978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2308755</t>
+          <t>2306260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2465560</t>
+          <t>2465112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2178956</t>
+          <t>2171348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2289422</t>
+          <t>2284620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2193818</t>
+          <t>2200868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2311464</t>
+          <t>2313907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4406940</t>
+          <t>4407388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4563745</t>
+          <t>4566240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36474</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>478837</t>
+          <t>519743</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466774</t>
+          <t>505587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487296</t>
+          <t>529556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>430045</t>
+          <t>467783</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422112</t>
+          <t>459464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435293</t>
+          <t>473965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>908881</t>
+          <t>987527</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>895787</t>
+          <t>974049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>918872</t>
+          <t>1000303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503248</t>
+          <t>548557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503248</t>
+          <t>548557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503248</t>
+          <t>548557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445118</t>
+          <t>486079</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445118</t>
+          <t>486079</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445118</t>
+          <t>486079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>948366</t>
+          <t>1034637</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>948366</t>
+          <t>1034637</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948366</t>
+          <t>1034637</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26821</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>28242</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>37603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54666</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>434083</t>
+          <t>464092</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424238</t>
+          <t>453622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441260</t>
+          <t>470966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>355996</t>
+          <t>392452</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346685</t>
+          <t>383091</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363451</t>
+          <t>400857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>790079</t>
+          <t>856544</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777181</t>
+          <t>844866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801237</t>
+          <t>868065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451059</t>
+          <t>481998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451059</t>
+          <t>481998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451059</t>
+          <t>481998</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380788</t>
+          <t>420694</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380788</t>
+          <t>420694</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380788</t>
+          <t>420694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>831847</t>
+          <t>902691</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>831847</t>
+          <t>902691</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>831847</t>
+          <t>902691</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>63353</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94388</t>
+          <t>80752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75068</t>
+          <t>85738</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32039</t>
+          <t>68757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110772</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>611755</t>
+          <t>407253</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573071</t>
+          <t>389854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646200</t>
+          <t>421821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146429</t>
+          <t>163924</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139188</t>
+          <t>155937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151841</t>
+          <t>170782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>758184</t>
+          <t>571177</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722480</t>
+          <t>554259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>801213</t>
+          <t>588158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667459</t>
+          <t>470606</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667459</t>
+          <t>470606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667459</t>
+          <t>470606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165793</t>
+          <t>186309</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165793</t>
+          <t>186309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165793</t>
+          <t>186309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833252</t>
+          <t>656915</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833252</t>
+          <t>656915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833252</t>
+          <t>656915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>156060</t>
+          <t>174480</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131912</t>
+          <t>149128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186070</t>
+          <t>202617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>120561</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>125027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159376</t>
+          <t>162980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>276622</t>
+          <t>316065</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186128</t>
+          <t>285049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321282</t>
+          <t>352108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>868884</t>
+          <t>945466</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838874</t>
+          <t>917329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893032</t>
+          <t>970818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>851803</t>
+          <t>713873</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>812988</t>
+          <t>692479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>908357</t>
+          <t>730432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1720686</t>
+          <t>1659340</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1676026</t>
+          <t>1623297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1811180</t>
+          <t>1690356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1024944</t>
+          <t>1119946</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024944</t>
+          <t>1119946</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1024944</t>
+          <t>1119946</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>972364</t>
+          <t>855459</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>972364</t>
+          <t>855459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>972364</t>
+          <t>855459</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1997308</t>
+          <t>1975405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1997308</t>
+          <t>1975405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1997308</t>
+          <t>1975405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>162903</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97665</t>
+          <t>141322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136005</t>
+          <t>185671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>280608</t>
+          <t>246232</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223549</t>
+          <t>224923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>420355</t>
+          <t>271909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>396162</t>
+          <t>409135</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336154</t>
+          <t>377450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>544307</t>
+          <t>444009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>352899</t>
+          <t>392385</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332448</t>
+          <t>369617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370788</t>
+          <t>413966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>522321</t>
+          <t>580121</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382574</t>
+          <t>554444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579380</t>
+          <t>601430</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>875220</t>
+          <t>972506</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>727075</t>
+          <t>937632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>935228</t>
+          <t>1004191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>468453</t>
+          <t>555288</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>468453</t>
+          <t>555288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468453</t>
+          <t>555288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>802929</t>
+          <t>826353</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>802929</t>
+          <t>826353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>802929</t>
+          <t>826353</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1271382</t>
+          <t>1381641</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1271382</t>
+          <t>1381641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1271382</t>
+          <t>1381641</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50793</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>130374</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>125694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151266</t>
+          <t>171793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>184286</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136672</t>
+          <t>158262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189004</t>
+          <t>215178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>191857</t>
+          <t>185469</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171101</t>
+          <t>164606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204780</t>
+          <t>200005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>617795</t>
+          <t>680322</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>596903</t>
+          <t>657705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>637250</t>
+          <t>703804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>809652</t>
+          <t>865792</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>781059</t>
+          <t>834900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833391</t>
+          <t>891816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>221894</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>221894</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>221894</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>748169</t>
+          <t>829498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>748169</t>
+          <t>829498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>748169</t>
+          <t>829498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>970063</t>
+          <t>1050078</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>970063</t>
+          <t>1050078</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>970063</t>
+          <t>1050078</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>398742</t>
+          <t>482566</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>308212</t>
+          <t>437814</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>451790</t>
+          <t>529411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>590773</t>
+          <t>605917</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>491675</t>
+          <t>564813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>787592</t>
+          <t>644657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>989515</t>
+          <t>1088483</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>866071</t>
+          <t>1028469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1186683</t>
+          <t>1153532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2938315</t>
+          <t>2914409</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2885267</t>
+          <t>2867564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3028845</t>
+          <t>2959161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,17 +10839,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2924388</t>
+          <t>2998476</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2727569</t>
+          <t>2959736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3023486</t>
+          <t>3039580</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5862703</t>
+          <t>5912885</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5665535</t>
+          <t>5847836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5986147</t>
+          <t>5972899</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3337057</t>
+          <t>3396975</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3337057</t>
+          <t>3396975</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3337057</t>
+          <t>3396975</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3515161</t>
+          <t>3604393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3515161</t>
+          <t>3604393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3515161</t>
+          <t>3604393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6852218</t>
+          <t>7001368</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6852218</t>
+          <t>7001368</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6852218</t>
+          <t>7001368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
